--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563200711</v>
+        <v>46157.93074880166</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93074880166</v>
+        <v>46157.93157645528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93157645528</v>
+        <v>46157.93394821944</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394821944</v>
+        <v>46157.93711347581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93711347581</v>
+        <v>46158.28211752076</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211752076</v>
+        <v>46158.29671259165</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29671259165</v>
+        <v>46158.29807678248</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807678248</v>
+        <v>46158.33382559436</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382559436</v>
+        <v>46158.36850135488</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36850135488</v>
+        <v>46158.37282679137</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
